--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -32,7 +32,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="113">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -43,7 +46,13 @@
     <t>Mid</t>
   </si>
   <si>
-    <t>TraitId</t>
+    <t>TraitIdList</t>
+  </si>
+  <si>
+    <t>TraitLevelList</t>
+  </si>
+  <si>
+    <t>TraitTypeList</t>
   </si>
   <si>
     <t>FlairIdList</t>
@@ -82,6 +91,9 @@
     <t>新手宠物</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>1,3</t>
   </si>
   <si>
@@ -149,6 +161,216 @@
   </si>
   <si>
     <t>30021,30024</t>
+  </si>
+  <si>
+    <t>经济流光</t>
+  </si>
+  <si>
+    <t>84,1001,1002</t>
+  </si>
+  <si>
+    <t>4,3,3</t>
+  </si>
+  <si>
+    <t>1,2,2</t>
+  </si>
+  <si>
+    <t>19,19,22,22</t>
+  </si>
+  <si>
+    <t>15,15,10,10</t>
+  </si>
+  <si>
+    <t>10021,10022,10023,10024</t>
+  </si>
+  <si>
+    <t>1002,1003,1005,1007</t>
+  </si>
+  <si>
+    <t>15,15,15,15</t>
+  </si>
+  <si>
+    <t>经济神雷</t>
+  </si>
+  <si>
+    <t>19,19,23,23</t>
+  </si>
+  <si>
+    <t>20021,20022,20023,20024</t>
+  </si>
+  <si>
+    <t>2002,2003,2005,2007</t>
+  </si>
+  <si>
+    <t>经济驱魔</t>
+  </si>
+  <si>
+    <t>19,19,24,24</t>
+  </si>
+  <si>
+    <t>30021,30022,30023,30024</t>
+  </si>
+  <si>
+    <t>3002,3003,3005,3007</t>
+  </si>
+  <si>
+    <t>经济剑网</t>
+  </si>
+  <si>
+    <t>10031,10032,10034,10051</t>
+  </si>
+  <si>
+    <t>经济火狱</t>
+  </si>
+  <si>
+    <t>20031,20032,20034,20051</t>
+  </si>
+  <si>
+    <t>经济剧毒</t>
+  </si>
+  <si>
+    <t>30031,30032,30034,30051</t>
+  </si>
+  <si>
+    <t>经济武盾</t>
+  </si>
+  <si>
+    <t>10051,10052,10061,10041</t>
+  </si>
+  <si>
+    <t>1002,1004,1005,1006</t>
+  </si>
+  <si>
+    <t>经济法盾</t>
+  </si>
+  <si>
+    <t>20051,20052,20061,20041</t>
+  </si>
+  <si>
+    <t>2002,2004,2005,2006</t>
+  </si>
+  <si>
+    <t>经济道盾</t>
+  </si>
+  <si>
+    <t>30051,30052,30061,30041</t>
+  </si>
+  <si>
+    <t>3002,3004,3005,3006</t>
+  </si>
+  <si>
+    <t>经济火麟</t>
+  </si>
+  <si>
+    <t>10071,10072,10073,10042</t>
+  </si>
+  <si>
+    <t>1002,1003,1004,1007</t>
+  </si>
+  <si>
+    <t>经济冰爆</t>
+  </si>
+  <si>
+    <t>20071,20072,20073,20042</t>
+  </si>
+  <si>
+    <t>2002,2003,2004,2007</t>
+  </si>
+  <si>
+    <t>经济英灵</t>
+  </si>
+  <si>
+    <t>30071,30072,30073,30042</t>
+  </si>
+  <si>
+    <t>3002,3003,3004,3007</t>
+  </si>
+  <si>
+    <t>速攻流光</t>
+  </si>
+  <si>
+    <t>11,1009,1016</t>
+  </si>
+  <si>
+    <t>4,3,2</t>
+  </si>
+  <si>
+    <t>速攻神雷</t>
+  </si>
+  <si>
+    <t>11,1009,1004</t>
+  </si>
+  <si>
+    <t>速攻驱魔</t>
+  </si>
+  <si>
+    <t>速攻剑网</t>
+  </si>
+  <si>
+    <t>速攻火狱</t>
+  </si>
+  <si>
+    <t>速攻剧毒</t>
+  </si>
+  <si>
+    <t>速攻武盾</t>
+  </si>
+  <si>
+    <t>速攻法盾</t>
+  </si>
+  <si>
+    <t>速攻道盾</t>
+  </si>
+  <si>
+    <t>速攻火麟</t>
+  </si>
+  <si>
+    <t>速攻冰爆</t>
+  </si>
+  <si>
+    <t>速攻英灵</t>
+  </si>
+  <si>
+    <t>攻攻流光</t>
+  </si>
+  <si>
+    <t>攻攻神雷</t>
+  </si>
+  <si>
+    <t>攻攻驱魔</t>
+  </si>
+  <si>
+    <t>攻攻剑网</t>
+  </si>
+  <si>
+    <t>攻攻火狱</t>
+  </si>
+  <si>
+    <t>攻攻剧毒</t>
+  </si>
+  <si>
+    <t>攻攻武盾</t>
+  </si>
+  <si>
+    <t>攻攻法盾</t>
+  </si>
+  <si>
+    <t>攻攻道盾</t>
+  </si>
+  <si>
+    <t>攻攻火麟</t>
+  </si>
+  <si>
+    <t>攻攻冰爆</t>
+  </si>
+  <si>
+    <t>攻攻英灵</t>
+  </si>
+  <si>
+    <t>不死固守</t>
+  </si>
+  <si>
+    <t>11,1008,1017</t>
   </si>
 </sst>
 </file>
@@ -805,6 +1027,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1125,147 +1348,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:P133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="14" style="1" customWidth="1"/>
-    <col min="7" max="7" width="29.0833333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="24.5" style="2" customWidth="1"/>
-    <col min="10" max="11" width="20.3333333333333" style="2" customWidth="1"/>
-    <col min="12" max="13" width="13.5" style="2" customWidth="1"/>
-    <col min="14" max="16372" width="9" style="3"/>
-    <col min="16373" max="16384" width="9" style="2"/>
+    <col min="4" max="8" width="14" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="35.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="24.5" style="2" customWidth="1"/>
+    <col min="12" max="13" width="20.3333333333333" style="2" customWidth="1"/>
+    <col min="14" max="15" width="13.5" style="2" customWidth="1"/>
+    <col min="16" max="16374" width="9" style="3"/>
+    <col min="16375" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>11</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:13">
+        <v>17</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
@@ -1274,33 +1521,39 @@
         <v>1</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="2">
+      <c r="J6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="2">
         <v>1</v>
       </c>
-      <c r="M6" s="2">
+      <c r="O6" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E7" s="6">
         <v>1</v>
@@ -1309,33 +1562,39 @@
         <v>1</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="K7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="2">
         <v>2</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
@@ -1344,33 +1603,39 @@
         <v>1</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="N8" s="2">
         <v>3</v>
       </c>
-      <c r="M8" s="2">
+      <c r="O8" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E9" s="6">
         <v>2</v>
@@ -1379,33 +1644,39 @@
         <v>3</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="2">
+      <c r="J9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="2">
         <v>1</v>
       </c>
-      <c r="M9" s="2">
+      <c r="O9" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
@@ -1414,33 +1685,39 @@
         <v>3</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="K10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="2">
         <v>2</v>
       </c>
-      <c r="M10" s="2">
+      <c r="O10" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C11" s="2">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E11" s="6">
         <v>2</v>
@@ -1449,33 +1726,39 @@
         <v>3</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="2">
+      <c r="N11" s="2">
         <v>3</v>
       </c>
-      <c r="M11" s="2">
+      <c r="O11" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C12" s="2">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E12" s="6">
         <v>3</v>
@@ -1484,33 +1767,39 @@
         <v>3</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="2">
+      <c r="J12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="2">
         <v>1</v>
       </c>
-      <c r="M12" s="2">
+      <c r="O12" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E13" s="6">
         <v>3</v>
@@ -1519,33 +1808,39 @@
         <v>3</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="2">
+      <c r="J13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" s="2">
         <v>2</v>
       </c>
-      <c r="M13" s="2">
+      <c r="O13" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:13">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:16">
       <c r="C14" s="2">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E14" s="6">
         <v>3</v>
@@ -1554,166 +1849,1801 @@
         <v>3</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="M14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="2">
+      <c r="N14" s="2">
         <v>3</v>
       </c>
-      <c r="M14" s="2">
+      <c r="O14" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1"/>
     <row r="16" s="2" customFormat="1" customHeight="1"/>
-    <row r="17" s="2" customFormat="1" customHeight="1"/>
-    <row r="18" s="2" customFormat="1" customHeight="1"/>
-    <row r="19" s="2" customFormat="1" customHeight="1"/>
-    <row r="20" s="2" customFormat="1" customHeight="1"/>
-    <row r="21" s="2" customFormat="1" customHeight="1"/>
-    <row r="22" s="2" customFormat="1" customHeight="1"/>
-    <row r="23" s="2" customFormat="1" customHeight="1"/>
-    <row r="24" s="2" customFormat="1" customHeight="1"/>
-    <row r="25" s="2" customFormat="1" customHeight="1"/>
-    <row r="26" s="2" customFormat="1" customHeight="1"/>
-    <row r="27" s="2" customFormat="1" customHeight="1"/>
-    <row r="28" s="2" customFormat="1" customHeight="1"/>
-    <row r="29" s="2" customFormat="1" customHeight="1"/>
-    <row r="30" s="2" customFormat="1" customHeight="1"/>
-    <row r="31" s="2" customFormat="1" customHeight="1"/>
-    <row r="32" s="2" customFormat="1" customHeight="1"/>
-    <row r="33" s="2" customFormat="1" customHeight="1"/>
-    <row r="34" s="2" customFormat="1" customHeight="1"/>
-    <row r="35" s="2" customFormat="1" customHeight="1"/>
-    <row r="36" s="2" customFormat="1" customHeight="1"/>
-    <row r="37" s="2" customFormat="1" customHeight="1"/>
-    <row r="38" s="2" customFormat="1" customHeight="1"/>
-    <row r="39" s="2" customFormat="1" customHeight="1"/>
-    <row r="40" s="2" customFormat="1" customHeight="1"/>
-    <row r="41" s="2" customFormat="1" customHeight="1"/>
-    <row r="42" s="2" customFormat="1" customHeight="1"/>
-    <row r="43" s="2" customFormat="1" customHeight="1"/>
-    <row r="44" s="2" customFormat="1" customHeight="1"/>
-    <row r="45" s="2" customFormat="1" customHeight="1"/>
-    <row r="46" s="2" customFormat="1" customHeight="1"/>
-    <row r="47" s="2" customFormat="1" customHeight="1"/>
-    <row r="48" s="2" customFormat="1" customHeight="1"/>
-    <row r="49" s="2" customFormat="1" customHeight="1"/>
-    <row r="50" s="2" customFormat="1" customHeight="1"/>
-    <row r="51" s="2" customFormat="1" customHeight="1"/>
-    <row r="52" s="2" customFormat="1" customHeight="1"/>
-    <row r="53" s="2" customFormat="1" customHeight="1"/>
-    <row r="54" s="2" customFormat="1" customHeight="1"/>
-    <row r="55" s="2" customFormat="1" customHeight="1"/>
-    <row r="56" s="2" customFormat="1" customHeight="1"/>
-    <row r="57" s="2" customFormat="1" customHeight="1"/>
-    <row r="58" s="2" customFormat="1" customHeight="1"/>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C17" s="2">
+        <v>101</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2">
+        <v>73</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="2">
+        <v>1</v>
+      </c>
+      <c r="O17" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C18" s="2">
+        <v>102</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="2">
+        <v>73</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="2">
+        <v>2</v>
+      </c>
+      <c r="O18" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C19" s="2">
+        <v>103</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2">
+        <v>73</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="2">
+        <v>3</v>
+      </c>
+      <c r="O19" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C20" s="2">
+        <v>104</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="2">
+        <v>73</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="2">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C21" s="2">
+        <v>105</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="2">
+        <v>73</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="2">
+        <v>2</v>
+      </c>
+      <c r="O21" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C22" s="2">
+        <v>106</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="2">
+        <v>73</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="2">
+        <v>3</v>
+      </c>
+      <c r="O22" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C23" s="2">
+        <v>107</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="2">
+        <v>73</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="2">
+        <v>1</v>
+      </c>
+      <c r="O23" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C24" s="2">
+        <v>108</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>73</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="2">
+        <v>2</v>
+      </c>
+      <c r="O24" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C25" s="2">
+        <v>109</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="2">
+        <v>73</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="2">
+        <v>3</v>
+      </c>
+      <c r="O25" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C26" s="2">
+        <v>110</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="2">
+        <v>73</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="2">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C27" s="2">
+        <v>111</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="2">
+        <v>73</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="2">
+        <v>2</v>
+      </c>
+      <c r="O27" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C28" s="2">
+        <v>112</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="2">
+        <v>73</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="2">
+        <v>3</v>
+      </c>
+      <c r="O28" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C30" s="2">
+        <v>201</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="2">
+        <v>73</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="2">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C31" s="2">
+        <v>202</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="2">
+        <v>73</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="2">
+        <v>2</v>
+      </c>
+      <c r="O31" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C32" s="2">
+        <v>203</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="2">
+        <v>73</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="2">
+        <v>3</v>
+      </c>
+      <c r="O32" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C33" s="2">
+        <v>204</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="2">
+        <v>73</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="2">
+        <v>1</v>
+      </c>
+      <c r="O33" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C34" s="2">
+        <v>205</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="2">
+        <v>73</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="2">
+        <v>2</v>
+      </c>
+      <c r="O34" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C35" s="2">
+        <v>206</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="2">
+        <v>73</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="2">
+        <v>3</v>
+      </c>
+      <c r="O35" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C36" s="2">
+        <v>207</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" s="2">
+        <v>73</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="2">
+        <v>1</v>
+      </c>
+      <c r="O36" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C37" s="2">
+        <v>208</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="2">
+        <v>73</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="2">
+        <v>2</v>
+      </c>
+      <c r="O37" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C38" s="2">
+        <v>209</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="2">
+        <v>73</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="2">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C39" s="2">
+        <v>210</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="2">
+        <v>73</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="2">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C40" s="2">
+        <v>211</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="2">
+        <v>73</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2</v>
+      </c>
+      <c r="O40" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C41" s="2">
+        <v>212</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="2">
+        <v>73</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="2">
+        <v>3</v>
+      </c>
+      <c r="O41" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C43" s="2">
+        <v>301</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" s="2">
+        <v>73</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="2">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C44" s="2">
+        <v>302</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E44" s="2">
+        <v>73</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="2">
+        <v>2</v>
+      </c>
+      <c r="O44" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C45" s="2">
+        <v>303</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" s="2">
+        <v>73</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="2">
+        <v>3</v>
+      </c>
+      <c r="O45" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C46" s="2">
+        <v>304</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="2">
+        <v>73</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="2">
+        <v>1</v>
+      </c>
+      <c r="O46" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C47" s="2">
+        <v>305</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="2">
+        <v>73</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="2">
+        <v>2</v>
+      </c>
+      <c r="O47" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C48" s="2">
+        <v>306</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E48" s="2">
+        <v>73</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="2">
+        <v>3</v>
+      </c>
+      <c r="O48" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C49" s="2">
+        <v>307</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E49" s="2">
+        <v>73</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="2">
+        <v>1</v>
+      </c>
+      <c r="O49" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C50" s="2">
+        <v>308</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E50" s="2">
+        <v>73</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="2">
+        <v>2</v>
+      </c>
+      <c r="O50" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C51" s="2">
+        <v>309</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E51" s="2">
+        <v>73</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="2">
+        <v>3</v>
+      </c>
+      <c r="O51" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C52" s="2">
+        <v>310</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E52" s="2">
+        <v>73</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="2">
+        <v>1</v>
+      </c>
+      <c r="O52" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C53" s="2">
+        <v>311</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" s="2">
+        <v>73</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="2">
+        <v>2</v>
+      </c>
+      <c r="O53" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C54" s="2">
+        <v>312</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E54" s="2">
+        <v>73</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="2">
+        <v>3</v>
+      </c>
+      <c r="O54" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A56" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="2">
+        <v>110</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E56" s="2">
+        <v>73</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="2">
+        <v>1</v>
+      </c>
+      <c r="O56" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A57" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="2">
+        <v>111</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E57" s="2">
+        <v>73</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="2">
+        <v>2</v>
+      </c>
+      <c r="O57" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="2">
+        <v>112</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E58" s="2">
+        <v>73</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="2">
+        <v>3</v>
+      </c>
+      <c r="O58" s="2">
+        <v>6</v>
+      </c>
+    </row>
     <row r="59" s="2" customFormat="1" customHeight="1"/>
     <row r="60" s="2" customFormat="1" customHeight="1"/>
-    <row r="61" customHeight="1" spans="3:7">
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" customHeight="1" spans="3:7">
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-    </row>
-    <row r="63" customHeight="1" spans="3:7">
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-    </row>
-    <row r="64" customHeight="1" spans="3:7">
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-    </row>
-    <row r="65" customHeight="1" spans="3:13">
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-    </row>
-    <row r="66" customHeight="1" spans="3:13">
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="76" customHeight="1" spans="3:13">
-      <c r="L76" s="6"/>
-      <c r="M76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="3:13">
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="3:13">
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="3:13">
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="3:13">
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="12:13">
-      <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="12:13">
-      <c r="L82" s="6"/>
-      <c r="M82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="12:13">
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="12:13">
-      <c r="L84" s="6"/>
-      <c r="M84" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="12:13">
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="12:13">
-      <c r="L102" s="6"/>
-      <c r="M102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="12:13">
-      <c r="L103" s="6"/>
-      <c r="M103" s="6"/>
+    <row r="61" s="2" customFormat="1" customHeight="1"/>
+    <row r="62" s="2" customFormat="1" customHeight="1"/>
+    <row r="63" s="2" customFormat="1" customHeight="1"/>
+    <row r="64" s="2" customFormat="1" customHeight="1"/>
+    <row r="65" s="2" customFormat="1" customHeight="1"/>
+    <row r="66" s="2" customFormat="1" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" customHeight="1"/>
+    <row r="68" s="2" customFormat="1" customHeight="1"/>
+    <row r="69" s="2" customFormat="1" customHeight="1"/>
+    <row r="70" s="2" customFormat="1" customHeight="1"/>
+    <row r="71" s="2" customFormat="1" customHeight="1"/>
+    <row r="72" s="2" customFormat="1" customHeight="1"/>
+    <row r="73" s="2" customFormat="1" customHeight="1"/>
+    <row r="74" s="2" customFormat="1" customHeight="1"/>
+    <row r="75" s="2" customFormat="1" customHeight="1"/>
+    <row r="76" s="2" customFormat="1" customHeight="1"/>
+    <row r="77" s="2" customFormat="1" customHeight="1"/>
+    <row r="78" s="2" customFormat="1" customHeight="1"/>
+    <row r="79" s="2" customFormat="1" customHeight="1"/>
+    <row r="80" s="2" customFormat="1" customHeight="1"/>
+    <row r="81" s="2" customFormat="1" customHeight="1"/>
+    <row r="82" s="2" customFormat="1" customHeight="1"/>
+    <row r="83" s="2" customFormat="1" customHeight="1"/>
+    <row r="84" s="2" customFormat="1" customHeight="1"/>
+    <row r="85" s="2" customFormat="1" customHeight="1"/>
+    <row r="86" s="2" customFormat="1" customHeight="1"/>
+    <row r="87" s="2" customFormat="1" customHeight="1"/>
+    <row r="88" s="2" customFormat="1" customHeight="1"/>
+    <row r="89" s="2" customFormat="1" customHeight="1"/>
+    <row r="90" s="2" customFormat="1" customHeight="1"/>
+    <row r="91" customHeight="1" spans="3:9">
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+    </row>
+    <row r="92" customHeight="1" spans="3:9">
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+    </row>
+    <row r="93" customHeight="1" spans="3:9">
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+    </row>
+    <row r="94" customHeight="1" spans="3:9">
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+    </row>
+    <row r="95" customHeight="1" spans="3:9">
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+    </row>
+    <row r="96" customHeight="1" spans="3:9">
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+    </row>
+    <row r="106" customHeight="1" spans="14:15">
+      <c r="N106" s="6"/>
+      <c r="O106" s="6"/>
+    </row>
+    <row r="107" customHeight="1" spans="14:15">
+      <c r="N107" s="6"/>
+      <c r="O107" s="6"/>
+    </row>
+    <row r="108" customHeight="1" spans="14:15">
+      <c r="N108" s="6"/>
+      <c r="O108" s="6"/>
+    </row>
+    <row r="109" customHeight="1" spans="14:15">
+      <c r="N109" s="6"/>
+      <c r="O109" s="6"/>
+    </row>
+    <row r="110" customHeight="1" spans="14:15">
+      <c r="N110" s="6"/>
+      <c r="O110" s="6"/>
+    </row>
+    <row r="111" customHeight="1" spans="14:15">
+      <c r="N111" s="6"/>
+      <c r="O111" s="6"/>
+    </row>
+    <row r="112" customHeight="1" spans="14:15">
+      <c r="N112" s="6"/>
+      <c r="O112" s="6"/>
+    </row>
+    <row r="113" customHeight="1" spans="14:15">
+      <c r="N113" s="6"/>
+      <c r="O113" s="6"/>
+    </row>
+    <row r="114" customHeight="1" spans="14:15">
+      <c r="N114" s="6"/>
+      <c r="O114" s="6"/>
+    </row>
+    <row r="131" customHeight="1" spans="14:15">
+      <c r="N131" s="6"/>
+      <c r="O131" s="6"/>
+    </row>
+    <row r="132" customHeight="1" spans="14:15">
+      <c r="N132" s="6"/>
+      <c r="O132" s="6"/>
+    </row>
+    <row r="133" customHeight="1" spans="14:15">
+      <c r="N133" s="6"/>
+      <c r="O133" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M3 C4:E4 F4 G4:M4 C5:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="105">
   <si>
     <t>#</t>
   </si>
@@ -166,16 +166,16 @@
     <t>经济流光</t>
   </si>
   <si>
-    <t>84,1001,1002</t>
+    <t>84,1011,1012</t>
   </si>
   <si>
     <t>4,3,3</t>
   </si>
   <si>
-    <t>1,2,2</t>
-  </si>
-  <si>
-    <t>19,19,22,22</t>
+    <t>2,2,2</t>
+  </si>
+  <si>
+    <t>20,20,22,22</t>
   </si>
   <si>
     <t>15,15,10,10</t>
@@ -193,7 +193,7 @@
     <t>经济神雷</t>
   </si>
   <si>
-    <t>19,19,23,23</t>
+    <t>20,20,23,23</t>
   </si>
   <si>
     <t>20021,20022,20023,20024</t>
@@ -205,7 +205,7 @@
     <t>经济驱魔</t>
   </si>
   <si>
-    <t>19,19,24,24</t>
+    <t>20,20,24,24</t>
   </si>
   <si>
     <t>30021,30022,30023,30024</t>
@@ -217,154 +217,130 @@
     <t>经济剑网</t>
   </si>
   <si>
-    <t>10031,10032,10034,10051</t>
+    <t>10031,10032,10034,10012</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1007</t>
   </si>
   <si>
     <t>经济火狱</t>
   </si>
   <si>
-    <t>20031,20032,20034,20051</t>
+    <t>20031,20032,20034,20012</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2007</t>
   </si>
   <si>
     <t>经济剧毒</t>
   </si>
   <si>
-    <t>30031,30032,30034,30051</t>
+    <t>30031,30032,30034,30032</t>
+  </si>
+  <si>
+    <t>3001,3002,3003,3007</t>
   </si>
   <si>
     <t>经济武盾</t>
   </si>
   <si>
-    <t>10051,10052,10061,10041</t>
-  </si>
-  <si>
-    <t>1002,1004,1005,1006</t>
+    <t>10051,10052,10041,10042</t>
+  </si>
+  <si>
+    <t>1002,1003,1004,1005</t>
   </si>
   <si>
     <t>经济法盾</t>
   </si>
   <si>
-    <t>20051,20052,20061,20041</t>
-  </si>
-  <si>
-    <t>2002,2004,2005,2006</t>
+    <t>20051,20052,20041,20042</t>
+  </si>
+  <si>
+    <t>2002,2003,2004,2005</t>
   </si>
   <si>
     <t>经济道盾</t>
   </si>
   <si>
-    <t>30051,30052,30061,30041</t>
-  </si>
-  <si>
-    <t>3002,3004,3005,3006</t>
+    <t>30051,30052,30041,30042</t>
+  </si>
+  <si>
+    <t>3002,3003,3004,3005</t>
   </si>
   <si>
     <t>经济火麟</t>
   </si>
   <si>
-    <t>10071,10072,10073,10042</t>
-  </si>
-  <si>
-    <t>1002,1003,1004,1007</t>
+    <t>10071,10072,10073,10061</t>
+  </si>
+  <si>
+    <t>1002,1003,1006,1007</t>
   </si>
   <si>
     <t>经济冰爆</t>
   </si>
   <si>
-    <t>20071,20072,20073,20042</t>
-  </si>
-  <si>
-    <t>2002,2003,2004,2007</t>
+    <t>20071,20072,20073,20061</t>
+  </si>
+  <si>
+    <t>2002,2003,2006,2007</t>
   </si>
   <si>
     <t>经济英灵</t>
   </si>
   <si>
-    <t>30071,30072,30073,30042</t>
-  </si>
-  <si>
-    <t>3002,3003,3004,3007</t>
-  </si>
-  <si>
-    <t>速攻流光</t>
-  </si>
-  <si>
-    <t>11,1009,1016</t>
-  </si>
-  <si>
-    <t>4,3,2</t>
-  </si>
-  <si>
-    <t>速攻神雷</t>
-  </si>
-  <si>
-    <t>11,1009,1004</t>
-  </si>
-  <si>
-    <t>速攻驱魔</t>
-  </si>
-  <si>
-    <t>速攻剑网</t>
-  </si>
-  <si>
-    <t>速攻火狱</t>
-  </si>
-  <si>
-    <t>速攻剧毒</t>
-  </si>
-  <si>
-    <t>速攻武盾</t>
-  </si>
-  <si>
-    <t>速攻法盾</t>
-  </si>
-  <si>
-    <t>速攻道盾</t>
-  </si>
-  <si>
-    <t>速攻火麟</t>
-  </si>
-  <si>
-    <t>速攻冰爆</t>
-  </si>
-  <si>
-    <t>速攻英灵</t>
-  </si>
-  <si>
-    <t>攻攻流光</t>
-  </si>
-  <si>
-    <t>攻攻神雷</t>
-  </si>
-  <si>
-    <t>攻攻驱魔</t>
-  </si>
-  <si>
-    <t>攻攻剑网</t>
-  </si>
-  <si>
-    <t>攻攻火狱</t>
-  </si>
-  <si>
-    <t>攻攻剧毒</t>
-  </si>
-  <si>
-    <t>攻攻武盾</t>
-  </si>
-  <si>
-    <t>攻攻法盾</t>
-  </si>
-  <si>
-    <t>攻攻道盾</t>
-  </si>
-  <si>
-    <t>攻攻火麟</t>
-  </si>
-  <si>
-    <t>攻攻冰爆</t>
-  </si>
-  <si>
-    <t>攻攻英灵</t>
+    <t>30071,30072,30073,30061</t>
+  </si>
+  <si>
+    <t>3002,3003,3006,3007</t>
+  </si>
+  <si>
+    <t>输出流光</t>
+  </si>
+  <si>
+    <t>28,1009,1016</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>输出神雷</t>
+  </si>
+  <si>
+    <t>29,1009,1004</t>
+  </si>
+  <si>
+    <t>输出驱魔</t>
+  </si>
+  <si>
+    <t>30,1009,1004</t>
+  </si>
+  <si>
+    <t>输出剑网</t>
+  </si>
+  <si>
+    <t>输出火狱</t>
+  </si>
+  <si>
+    <t>输出剧毒</t>
+  </si>
+  <si>
+    <t>输出武盾</t>
+  </si>
+  <si>
+    <t>输出法盾</t>
+  </si>
+  <si>
+    <t>输出道盾</t>
+  </si>
+  <si>
+    <t>输出火麟</t>
+  </si>
+  <si>
+    <t>输出冰爆</t>
+  </si>
+  <si>
+    <t>输出英灵</t>
   </si>
   <si>
     <t>不死固守</t>
@@ -2030,7 +2006,7 @@
         <v>61</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M20" s="8" t="s">
         <v>51</v>
@@ -2047,7 +2023,7 @@
         <v>105</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2">
         <v>73</v>
@@ -2068,10 +2044,10 @@
         <v>48</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>51</v>
@@ -2088,7 +2064,7 @@
         <v>106</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2">
         <v>73</v>
@@ -2109,10 +2085,10 @@
         <v>48</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M22" s="8" t="s">
         <v>51</v>
@@ -2129,7 +2105,7 @@
         <v>107</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E23" s="2">
         <v>73</v>
@@ -2150,10 +2126,10 @@
         <v>48</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M23" s="8" t="s">
         <v>51</v>
@@ -2170,7 +2146,7 @@
         <v>108</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2">
         <v>73</v>
@@ -2191,10 +2167,10 @@
         <v>48</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M24" s="8" t="s">
         <v>51</v>
@@ -2211,7 +2187,7 @@
         <v>109</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2">
         <v>73</v>
@@ -2232,10 +2208,10 @@
         <v>48</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M25" s="8" t="s">
         <v>51</v>
@@ -2252,7 +2228,7 @@
         <v>110</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2">
         <v>73</v>
@@ -2273,10 +2249,10 @@
         <v>48</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M26" s="8" t="s">
         <v>51</v>
@@ -2293,7 +2269,7 @@
         <v>111</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2">
         <v>73</v>
@@ -2314,10 +2290,10 @@
         <v>48</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M27" s="8" t="s">
         <v>51</v>
@@ -2334,7 +2310,7 @@
         <v>112</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2">
         <v>73</v>
@@ -2355,10 +2331,10 @@
         <v>48</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M28" s="8" t="s">
         <v>51</v>
@@ -2380,16 +2356,16 @@
         <v>201</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E30" s="2">
         <v>73</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>46</v>
@@ -2421,16 +2397,16 @@
         <v>202</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E31" s="2">
         <v>73</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>46</v>
@@ -2462,16 +2438,16 @@
         <v>203</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E32" s="2">
         <v>73</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>46</v>
@@ -2503,16 +2479,16 @@
         <v>204</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E33" s="2">
         <v>73</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>46</v>
@@ -2527,7 +2503,7 @@
         <v>61</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M33" s="8" t="s">
         <v>51</v>
@@ -2544,16 +2520,16 @@
         <v>205</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E34" s="2">
         <v>73</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>46</v>
@@ -2565,10 +2541,10 @@
         <v>48</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M34" s="8" t="s">
         <v>51</v>
@@ -2585,16 +2561,16 @@
         <v>206</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E35" s="2">
         <v>73</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>46</v>
@@ -2606,10 +2582,10 @@
         <v>48</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M35" s="8" t="s">
         <v>51</v>
@@ -2626,16 +2602,16 @@
         <v>207</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E36" s="2">
         <v>73</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>46</v>
@@ -2647,10 +2623,10 @@
         <v>48</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M36" s="8" t="s">
         <v>51</v>
@@ -2667,16 +2643,16 @@
         <v>208</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E37" s="2">
         <v>73</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>46</v>
@@ -2688,10 +2664,10 @@
         <v>48</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M37" s="8" t="s">
         <v>51</v>
@@ -2708,16 +2684,16 @@
         <v>209</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E38" s="2">
         <v>73</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>46</v>
@@ -2729,10 +2705,10 @@
         <v>48</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M38" s="8" t="s">
         <v>51</v>
@@ -2749,16 +2725,16 @@
         <v>210</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E39" s="2">
         <v>73</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>46</v>
@@ -2770,10 +2746,10 @@
         <v>48</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M39" s="8" t="s">
         <v>51</v>
@@ -2790,16 +2766,16 @@
         <v>211</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E40" s="2">
         <v>73</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>46</v>
@@ -2811,10 +2787,10 @@
         <v>48</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>51</v>
@@ -2831,16 +2807,16 @@
         <v>212</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E41" s="2">
         <v>73</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>46</v>
@@ -2852,10 +2828,10 @@
         <v>48</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M41" s="8" t="s">
         <v>51</v>
@@ -2871,496 +2847,52 @@
       <c r="H42" s="6"/>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C43" s="2">
-        <v>301</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E43" s="2">
-        <v>73</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N43" s="2">
-        <v>1</v>
-      </c>
-      <c r="O43" s="2">
-        <v>6</v>
-      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C44" s="2">
-        <v>302</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E44" s="2">
-        <v>73</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M44" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N44" s="2">
-        <v>2</v>
-      </c>
-      <c r="O44" s="2">
-        <v>6</v>
-      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C45" s="2">
-        <v>303</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" s="2">
-        <v>73</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L45" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N45" s="2">
-        <v>3</v>
-      </c>
-      <c r="O45" s="2">
-        <v>6</v>
-      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C46" s="2">
-        <v>304</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E46" s="2">
-        <v>73</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L46" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="M46" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N46" s="2">
-        <v>1</v>
-      </c>
-      <c r="O46" s="2">
-        <v>6</v>
-      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C47" s="2">
-        <v>305</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="2">
-        <v>73</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="L47" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M47" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N47" s="2">
-        <v>2</v>
-      </c>
-      <c r="O47" s="2">
-        <v>6</v>
-      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C48" s="2">
-        <v>306</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E48" s="2">
-        <v>73</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="L48" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M48" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N48" s="2">
-        <v>3</v>
-      </c>
-      <c r="O48" s="2">
-        <v>6</v>
-      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C49" s="2">
-        <v>307</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E49" s="2">
-        <v>73</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L49" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N49" s="2">
-        <v>1</v>
-      </c>
-      <c r="O49" s="2">
-        <v>6</v>
-      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C50" s="2">
-        <v>308</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E50" s="2">
-        <v>73</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M50" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N50" s="2">
-        <v>2</v>
-      </c>
-      <c r="O50" s="2">
-        <v>6</v>
-      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C51" s="2">
-        <v>309</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E51" s="2">
-        <v>73</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L51" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N51" s="2">
-        <v>3</v>
-      </c>
-      <c r="O51" s="2">
-        <v>6</v>
-      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C52" s="2">
-        <v>310</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E52" s="2">
-        <v>73</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="M52" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N52" s="2">
-        <v>1</v>
-      </c>
-      <c r="O52" s="2">
-        <v>6</v>
-      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C53" s="2">
-        <v>311</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E53" s="2">
-        <v>73</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L53" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N53" s="2">
-        <v>2</v>
-      </c>
-      <c r="O53" s="2">
-        <v>6</v>
-      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C54" s="2">
-        <v>312</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E54" s="2">
-        <v>73</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="L54" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N54" s="2">
-        <v>3</v>
-      </c>
-      <c r="O54" s="2">
-        <v>6</v>
-      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="G55" s="6"/>
@@ -3377,13 +2909,13 @@
         <v>110</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E56" s="2">
         <v>73</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>45</v>
@@ -3424,13 +2956,13 @@
         <v>111</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E57" s="2">
         <v>73</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>45</v>
@@ -3471,13 +3003,13 @@
         <v>112</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E58" s="2">
         <v>73</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>45</v>
@@ -3643,7 +3175,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M3 C4:E4 F4 G4:M4 C5:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -253,7 +253,7 @@
     <t>经济法盾</t>
   </si>
   <si>
-    <t>20051,20052,20041,20042</t>
+    <t>20051,20052,20041,20043</t>
   </si>
   <si>
     <t>2002,2003,2004,2005</t>
@@ -262,7 +262,7 @@
     <t>经济道盾</t>
   </si>
   <si>
-    <t>30051,30052,30041,30042</t>
+    <t>30051,30052,30041,30043</t>
   </si>
   <si>
     <t>3002,3003,3004,3005</t>
@@ -289,7 +289,7 @@
     <t>经济英灵</t>
   </si>
   <si>
-    <t>30071,30072,30073,30061</t>
+    <t>30071,30073,30073,30061</t>
   </si>
   <si>
     <t>3002,3003,3006,3007</t>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -235,10 +235,10 @@
     <t>经济剧毒</t>
   </si>
   <si>
-    <t>30031,30032,30034,30032</t>
-  </si>
-  <si>
-    <t>3001,3002,3003,3007</t>
+    <t>30031,30032,30033,30034</t>
+  </si>
+  <si>
+    <t>3002,3003,3004,3007</t>
   </si>
   <si>
     <t>经济武盾</t>
@@ -289,10 +289,10 @@
     <t>经济英灵</t>
   </si>
   <si>
-    <t>30071,30073,30073,30061</t>
-  </si>
-  <si>
-    <t>3002,3003,3006,3007</t>
+    <t>30071,30073,30012,30061</t>
+  </si>
+  <si>
+    <t>3001,3002,3006,3007</t>
   </si>
   <si>
     <t>输出流光</t>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -181,172 +181,202 @@
     <t>15,15,10,10</t>
   </si>
   <si>
+    <t>10022,10023,10024</t>
+  </si>
+  <si>
+    <t>1002,1003,1005,1007</t>
+  </si>
+  <si>
+    <t>15,15,15,15</t>
+  </si>
+  <si>
+    <t>经济神雷</t>
+  </si>
+  <si>
+    <t>20,20,23,23</t>
+  </si>
+  <si>
+    <t>20022,20023,20024</t>
+  </si>
+  <si>
+    <t>2002,2003,2005,2007</t>
+  </si>
+  <si>
+    <t>经济驱魔</t>
+  </si>
+  <si>
+    <t>20,20,24,24</t>
+  </si>
+  <si>
+    <t>30022,30023,30024</t>
+  </si>
+  <si>
+    <t>3002,3003,3004,3005</t>
+  </si>
+  <si>
+    <t>经济剑网</t>
+  </si>
+  <si>
+    <t>10031,10032,10034</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1007</t>
+  </si>
+  <si>
+    <t>经济火狱</t>
+  </si>
+  <si>
+    <t>20031,20032,20034</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2007</t>
+  </si>
+  <si>
+    <t>经济剧毒</t>
+  </si>
+  <si>
+    <t>30032,30033,30034</t>
+  </si>
+  <si>
+    <t>经济蛮牛</t>
+  </si>
+  <si>
+    <t>10041,10042,10012</t>
+  </si>
+  <si>
+    <t>1001,1002,1003,1004</t>
+  </si>
+  <si>
+    <t>经济烈焰</t>
+  </si>
+  <si>
+    <t>20041,20043,20012</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2004</t>
+  </si>
+  <si>
+    <t>经济圣疗</t>
+  </si>
+  <si>
+    <t>30041,30043,30031</t>
+  </si>
+  <si>
+    <t>经济武盾</t>
+  </si>
+  <si>
+    <t>10051,10052,10061</t>
+  </si>
+  <si>
+    <t>1002,1003,1004,1005</t>
+  </si>
+  <si>
+    <t>经济法盾</t>
+  </si>
+  <si>
+    <t>20051,20052,20061</t>
+  </si>
+  <si>
+    <t>2002,2003,2004,2005</t>
+  </si>
+  <si>
+    <t>经济道盾</t>
+  </si>
+  <si>
+    <t>30051,30052,30061</t>
+  </si>
+  <si>
+    <t>3002,3003,3005,3006</t>
+  </si>
+  <si>
+    <t>经济火麟</t>
+  </si>
+  <si>
+    <t>10071,10072,10073</t>
+  </si>
+  <si>
+    <t>1002,1003,1006,1007</t>
+  </si>
+  <si>
+    <t>经济冰爆</t>
+  </si>
+  <si>
+    <t>20071,20072,20073</t>
+  </si>
+  <si>
+    <t>2002,2003,2006,2007</t>
+  </si>
+  <si>
+    <t>经济英灵</t>
+  </si>
+  <si>
+    <t>30071,30073,30012</t>
+  </si>
+  <si>
+    <t>输出流光</t>
+  </si>
+  <si>
+    <t>28,1009,1016</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>输出神雷</t>
+  </si>
+  <si>
+    <t>29,1009,1016</t>
+  </si>
+  <si>
+    <t>输出驱魔</t>
+  </si>
+  <si>
+    <t>30,1009,1016</t>
+  </si>
+  <si>
+    <t>输出剑网</t>
+  </si>
+  <si>
+    <t>输出火狱</t>
+  </si>
+  <si>
+    <t>输出剧毒</t>
+  </si>
+  <si>
+    <t>输出武盾</t>
+  </si>
+  <si>
+    <t>输出法盾</t>
+  </si>
+  <si>
+    <t>输出道盾</t>
+  </si>
+  <si>
+    <t>输出火麟</t>
+  </si>
+  <si>
+    <t>输出冰爆</t>
+  </si>
+  <si>
+    <t>输出英灵</t>
+  </si>
+  <si>
+    <t>不死固守</t>
+  </si>
+  <si>
+    <t>11,1008,1017</t>
+  </si>
+  <si>
     <t>10021,10022,10023,10024</t>
   </si>
   <si>
-    <t>1002,1003,1005,1007</t>
-  </si>
-  <si>
-    <t>15,15,15,15</t>
-  </si>
-  <si>
-    <t>经济神雷</t>
-  </si>
-  <si>
-    <t>20,20,23,23</t>
-  </si>
-  <si>
     <t>20021,20022,20023,20024</t>
   </si>
   <si>
-    <t>2002,2003,2005,2007</t>
-  </si>
-  <si>
-    <t>经济驱魔</t>
-  </si>
-  <si>
-    <t>20,20,24,24</t>
-  </si>
-  <si>
     <t>30021,30022,30023,30024</t>
   </si>
   <si>
     <t>3002,3003,3005,3007</t>
-  </si>
-  <si>
-    <t>经济剑网</t>
-  </si>
-  <si>
-    <t>10031,10032,10034,10012</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1007</t>
-  </si>
-  <si>
-    <t>经济火狱</t>
-  </si>
-  <si>
-    <t>20031,20032,20034,20012</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2007</t>
-  </si>
-  <si>
-    <t>经济剧毒</t>
-  </si>
-  <si>
-    <t>30031,30032,30033,30034</t>
-  </si>
-  <si>
-    <t>3002,3003,3004,3007</t>
-  </si>
-  <si>
-    <t>经济武盾</t>
-  </si>
-  <si>
-    <t>10051,10052,10041,10042</t>
-  </si>
-  <si>
-    <t>1002,1003,1004,1005</t>
-  </si>
-  <si>
-    <t>经济法盾</t>
-  </si>
-  <si>
-    <t>20051,20052,20041,20043</t>
-  </si>
-  <si>
-    <t>2002,2003,2004,2005</t>
-  </si>
-  <si>
-    <t>经济道盾</t>
-  </si>
-  <si>
-    <t>30051,30052,30041,30043</t>
-  </si>
-  <si>
-    <t>3002,3003,3004,3005</t>
-  </si>
-  <si>
-    <t>经济火麟</t>
-  </si>
-  <si>
-    <t>10071,10072,10073,10061</t>
-  </si>
-  <si>
-    <t>1002,1003,1006,1007</t>
-  </si>
-  <si>
-    <t>经济冰爆</t>
-  </si>
-  <si>
-    <t>20071,20072,20073,20061</t>
-  </si>
-  <si>
-    <t>2002,2003,2006,2007</t>
-  </si>
-  <si>
-    <t>经济英灵</t>
-  </si>
-  <si>
-    <t>30071,30073,30012,30061</t>
-  </si>
-  <si>
-    <t>3001,3002,3006,3007</t>
-  </si>
-  <si>
-    <t>输出流光</t>
-  </si>
-  <si>
-    <t>28,1009,1016</t>
-  </si>
-  <si>
-    <t>3,3,3</t>
-  </si>
-  <si>
-    <t>输出神雷</t>
-  </si>
-  <si>
-    <t>29,1009,1004</t>
-  </si>
-  <si>
-    <t>输出驱魔</t>
-  </si>
-  <si>
-    <t>30,1009,1004</t>
-  </si>
-  <si>
-    <t>输出剑网</t>
-  </si>
-  <si>
-    <t>输出火狱</t>
-  </si>
-  <si>
-    <t>输出剧毒</t>
-  </si>
-  <si>
-    <t>输出武盾</t>
-  </si>
-  <si>
-    <t>输出法盾</t>
-  </si>
-  <si>
-    <t>输出道盾</t>
-  </si>
-  <si>
-    <t>输出火麟</t>
-  </si>
-  <si>
-    <t>输出冰爆</t>
-  </si>
-  <si>
-    <t>输出英灵</t>
-  </si>
-  <si>
-    <t>不死固守</t>
-  </si>
-  <si>
-    <t>11,1008,1017</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1354,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P133"/>
+  <dimension ref="A1:P142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
@@ -2088,7 +2118,7 @@
         <v>67</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="M22" s="8" t="s">
         <v>51</v>
@@ -2105,7 +2135,7 @@
         <v>107</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2">
         <v>73</v>
@@ -2126,10 +2156,10 @@
         <v>48</v>
       </c>
       <c r="K23" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="M23" s="8" t="s">
         <v>51</v>
@@ -2146,7 +2176,7 @@
         <v>108</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2">
         <v>73</v>
@@ -2167,10 +2197,10 @@
         <v>48</v>
       </c>
       <c r="K24" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="M24" s="8" t="s">
         <v>51</v>
@@ -2187,7 +2217,7 @@
         <v>109</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" s="2">
         <v>73</v>
@@ -2208,10 +2238,10 @@
         <v>48</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M25" s="8" t="s">
         <v>51</v>
@@ -2228,7 +2258,7 @@
         <v>110</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2">
         <v>73</v>
@@ -2249,10 +2279,10 @@
         <v>48</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M26" s="8" t="s">
         <v>51</v>
@@ -2269,7 +2299,7 @@
         <v>111</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2">
         <v>73</v>
@@ -2290,10 +2320,10 @@
         <v>48</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M27" s="8" t="s">
         <v>51</v>
@@ -2310,7 +2340,7 @@
         <v>112</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2">
         <v>73</v>
@@ -2331,10 +2361,10 @@
         <v>48</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M28" s="8" t="s">
         <v>51</v>
@@ -2347,46 +2377,82 @@
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+      <c r="C29" s="2">
+        <v>113</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2">
+        <v>73</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="2">
+        <v>1</v>
+      </c>
+      <c r="O29" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="2">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E30" s="2">
         <v>73</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>89</v>
+      <c r="F30" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="M30" s="8" t="s">
         <v>51</v>
       </c>
       <c r="N30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2">
         <v>6</v>
@@ -2394,224 +2460,80 @@
     </row>
     <row r="31" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="2">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="2">
         <v>73</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>89</v>
+      <c r="F31" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M31" s="8" t="s">
         <v>51</v>
       </c>
       <c r="N31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O31" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C32" s="2">
-        <v>203</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="2">
-        <v>73</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N32" s="2">
-        <v>3</v>
-      </c>
-      <c r="O32" s="2">
-        <v>6</v>
-      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C33" s="2">
-        <v>204</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" s="2">
-        <v>73</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="M33" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="2">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2">
-        <v>6</v>
-      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C34" s="2">
-        <v>205</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" s="2">
-        <v>73</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N34" s="2">
-        <v>2</v>
-      </c>
-      <c r="O34" s="2">
-        <v>6</v>
-      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C35" s="2">
-        <v>206</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E35" s="2">
-        <v>73</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N35" s="2">
-        <v>3</v>
-      </c>
-      <c r="O35" s="2">
-        <v>6</v>
-      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C36" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E36" s="2">
         <v>73</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>46</v>
@@ -2623,10 +2545,10 @@
         <v>48</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="M36" s="8" t="s">
         <v>51</v>
@@ -2640,19 +2562,19 @@
     </row>
     <row r="37" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C37" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E37" s="2">
         <v>73</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>46</v>
@@ -2664,10 +2586,10 @@
         <v>48</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="M37" s="8" t="s">
         <v>51</v>
@@ -2681,19 +2603,19 @@
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C38" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E38" s="2">
         <v>73</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>46</v>
@@ -2705,10 +2627,10 @@
         <v>48</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M38" s="8" t="s">
         <v>51</v>
@@ -2722,7 +2644,7 @@
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C39" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>100</v>
@@ -2731,10 +2653,10 @@
         <v>73</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>46</v>
@@ -2746,10 +2668,10 @@
         <v>48</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="M39" s="8" t="s">
         <v>51</v>
@@ -2763,7 +2685,7 @@
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C40" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>101</v>
@@ -2772,10 +2694,10 @@
         <v>73</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>46</v>
@@ -2787,10 +2709,10 @@
         <v>48</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>51</v>
@@ -2804,7 +2726,7 @@
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C41" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>102</v>
@@ -2813,10 +2735,10 @@
         <v>73</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>46</v>
@@ -2828,10 +2750,10 @@
         <v>48</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="M41" s="8" t="s">
         <v>51</v>
@@ -2844,210 +2766,570 @@
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="H42" s="6"/>
+      <c r="C42" s="2">
+        <v>207</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="2">
+        <v>73</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="2">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
+      <c r="C43" s="2">
+        <v>208</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E43" s="2">
+        <v>73</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="2">
+        <v>2</v>
+      </c>
+      <c r="O43" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
+      <c r="C44" s="2">
+        <v>209</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="2">
+        <v>73</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="2">
+        <v>3</v>
+      </c>
+      <c r="O44" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
+      <c r="C45" s="2">
+        <v>210</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="2">
+        <v>73</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="2">
+        <v>1</v>
+      </c>
+      <c r="O45" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
+      <c r="C46" s="2">
+        <v>211</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E46" s="2">
+        <v>73</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="2">
+        <v>2</v>
+      </c>
+      <c r="O46" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
+      <c r="C47" s="2">
+        <v>212</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E47" s="2">
+        <v>73</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="2">
+        <v>3</v>
+      </c>
+      <c r="O47" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="G51" s="6"/>
+      <c r="C48" s="2">
+        <v>213</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" s="2">
+        <v>73</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="2">
+        <v>1</v>
+      </c>
+      <c r="O48" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C49" s="2">
+        <v>214</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" s="2">
+        <v>73</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="2">
+        <v>2</v>
+      </c>
+      <c r="O49" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C50" s="2">
+        <v>215</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="2">
+        <v>73</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="2">
+        <v>3</v>
+      </c>
+      <c r="O50" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="H51" s="6"/>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="1:15">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="1:15">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
     </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="1:15">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
     </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="1:15">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
     </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A56" s="2" t="s">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A65" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C65" s="2">
         <v>110</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E56" s="2">
+      <c r="D65" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E65" s="2">
         <v>73</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G56" s="7" t="s">
+      <c r="F65" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G65" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H56" s="7" t="s">
+      <c r="H65" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="I65" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="J65" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K56" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L56" s="8" t="s">
+      <c r="K65" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="L65" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="M56" s="8" t="s">
+      <c r="M65" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N56" s="2">
+      <c r="N65" s="2">
         <v>1</v>
       </c>
-      <c r="O56" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A57" s="2" t="s">
+      <c r="O65" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A66" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C66" s="2">
         <v>111</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E57" s="2">
+      <c r="D66" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" s="2">
         <v>73</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G57" s="7" t="s">
+      <c r="F66" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G66" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="H66" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="I66" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="J66" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K57" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L57" s="8" t="s">
+      <c r="K66" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="L66" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="M57" s="8" t="s">
+      <c r="M66" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N57" s="2">
+      <c r="N66" s="2">
         <v>2</v>
       </c>
-      <c r="O57" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A58" s="2" t="s">
+      <c r="O66" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A67" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C67" s="2">
         <v>112</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E58" s="2">
+      <c r="D67" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E67" s="2">
         <v>73</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G58" s="7" t="s">
+      <c r="F67" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G67" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="H67" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="I67" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="J67" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K58" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M58" s="8" t="s">
+      <c r="K67" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M67" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="N58" s="2">
+      <c r="N67" s="2">
         <v>3</v>
       </c>
-      <c r="O58" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" s="2" customFormat="1" customHeight="1"/>
-    <row r="60" s="2" customFormat="1" customHeight="1"/>
-    <row r="61" s="2" customFormat="1" customHeight="1"/>
-    <row r="62" s="2" customFormat="1" customHeight="1"/>
-    <row r="63" s="2" customFormat="1" customHeight="1"/>
-    <row r="64" s="2" customFormat="1" customHeight="1"/>
-    <row r="65" s="2" customFormat="1" customHeight="1"/>
-    <row r="66" s="2" customFormat="1" customHeight="1"/>
-    <row r="67" s="2" customFormat="1" customHeight="1"/>
+      <c r="O67" s="2">
+        <v>6</v>
+      </c>
+    </row>
     <row r="68" s="2" customFormat="1" customHeight="1"/>
     <row r="69" s="2" customFormat="1" customHeight="1"/>
     <row r="70" s="2" customFormat="1" customHeight="1"/>
@@ -3071,107 +3353,116 @@
     <row r="88" s="2" customFormat="1" customHeight="1"/>
     <row r="89" s="2" customFormat="1" customHeight="1"/>
     <row r="90" s="2" customFormat="1" customHeight="1"/>
-    <row r="91" customHeight="1" spans="3:9">
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-    </row>
-    <row r="92" customHeight="1" spans="3:9">
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-    </row>
-    <row r="93" customHeight="1" spans="3:9">
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-    </row>
-    <row r="94" customHeight="1" spans="3:9">
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-    </row>
-    <row r="95" customHeight="1" spans="3:9">
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-    </row>
-    <row r="96" customHeight="1" spans="3:9">
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-    </row>
-    <row r="106" customHeight="1" spans="14:15">
-      <c r="N106" s="6"/>
-      <c r="O106" s="6"/>
-    </row>
-    <row r="107" customHeight="1" spans="14:15">
-      <c r="N107" s="6"/>
-      <c r="O107" s="6"/>
-    </row>
-    <row r="108" customHeight="1" spans="14:15">
-      <c r="N108" s="6"/>
-      <c r="O108" s="6"/>
-    </row>
-    <row r="109" customHeight="1" spans="14:15">
-      <c r="N109" s="6"/>
-      <c r="O109" s="6"/>
-    </row>
-    <row r="110" customHeight="1" spans="14:15">
-      <c r="N110" s="6"/>
-      <c r="O110" s="6"/>
-    </row>
-    <row r="111" customHeight="1" spans="14:15">
-      <c r="N111" s="6"/>
-      <c r="O111" s="6"/>
-    </row>
-    <row r="112" customHeight="1" spans="14:15">
-      <c r="N112" s="6"/>
-      <c r="O112" s="6"/>
-    </row>
-    <row r="113" customHeight="1" spans="14:15">
-      <c r="N113" s="6"/>
-      <c r="O113" s="6"/>
-    </row>
-    <row r="114" customHeight="1" spans="14:15">
-      <c r="N114" s="6"/>
-      <c r="O114" s="6"/>
-    </row>
-    <row r="131" customHeight="1" spans="14:15">
-      <c r="N131" s="6"/>
-      <c r="O131" s="6"/>
-    </row>
-    <row r="132" customHeight="1" spans="14:15">
-      <c r="N132" s="6"/>
-      <c r="O132" s="6"/>
-    </row>
-    <row r="133" customHeight="1" spans="14:15">
-      <c r="N133" s="6"/>
-      <c r="O133" s="6"/>
+    <row r="91" s="2" customFormat="1" customHeight="1"/>
+    <row r="92" s="2" customFormat="1" customHeight="1"/>
+    <row r="93" s="2" customFormat="1" customHeight="1"/>
+    <row r="94" s="2" customFormat="1" customHeight="1"/>
+    <row r="95" s="2" customFormat="1" customHeight="1"/>
+    <row r="96" s="2" customFormat="1" customHeight="1"/>
+    <row r="97" s="2" customFormat="1" customHeight="1"/>
+    <row r="98" s="2" customFormat="1" customHeight="1"/>
+    <row r="99" s="2" customFormat="1" customHeight="1"/>
+    <row r="100" customHeight="1" spans="3:9">
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+    </row>
+    <row r="101" customHeight="1" spans="3:9">
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+    </row>
+    <row r="102" customHeight="1" spans="3:9">
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+    </row>
+    <row r="103" customHeight="1" spans="3:9">
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+    </row>
+    <row r="104" customHeight="1" spans="3:9">
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+    </row>
+    <row r="105" customHeight="1" spans="3:9">
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+    </row>
+    <row r="115" customHeight="1" spans="14:15">
+      <c r="N115" s="6"/>
+      <c r="O115" s="6"/>
+    </row>
+    <row r="116" customHeight="1" spans="14:15">
+      <c r="N116" s="6"/>
+      <c r="O116" s="6"/>
+    </row>
+    <row r="117" customHeight="1" spans="14:15">
+      <c r="N117" s="6"/>
+      <c r="O117" s="6"/>
+    </row>
+    <row r="118" customHeight="1" spans="14:15">
+      <c r="N118" s="6"/>
+      <c r="O118" s="6"/>
+    </row>
+    <row r="119" customHeight="1" spans="14:15">
+      <c r="N119" s="6"/>
+      <c r="O119" s="6"/>
+    </row>
+    <row r="120" customHeight="1" spans="14:15">
+      <c r="N120" s="6"/>
+      <c r="O120" s="6"/>
+    </row>
+    <row r="121" customHeight="1" spans="14:15">
+      <c r="N121" s="6"/>
+      <c r="O121" s="6"/>
+    </row>
+    <row r="122" customHeight="1" spans="14:15">
+      <c r="N122" s="6"/>
+      <c r="O122" s="6"/>
+    </row>
+    <row r="123" customHeight="1" spans="14:15">
+      <c r="N123" s="6"/>
+      <c r="O123" s="6"/>
+    </row>
+    <row r="140" customHeight="1" spans="14:15">
+      <c r="N140" s="6"/>
+      <c r="O140" s="6"/>
+    </row>
+    <row r="141" customHeight="1" spans="14:15">
+      <c r="N141" s="6"/>
+      <c r="O141" s="6"/>
+    </row>
+    <row r="142" customHeight="1" spans="14:15">
+      <c r="N142" s="6"/>
+      <c r="O142" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="122">
   <si>
     <t>#</t>
   </si>
@@ -361,22 +361,43 @@
     <t>输出英灵</t>
   </si>
   <si>
-    <t>不死固守</t>
-  </si>
-  <si>
-    <t>11,1008,1017</t>
-  </si>
-  <si>
-    <t>10021,10022,10023,10024</t>
-  </si>
-  <si>
-    <t>20021,20022,20023,20024</t>
-  </si>
-  <si>
-    <t>30021,30022,30023,30024</t>
-  </si>
-  <si>
-    <t>3002,3003,3005,3007</t>
+    <t>生存流光</t>
+  </si>
+  <si>
+    <t>33,1007,1008</t>
+  </si>
+  <si>
+    <t>生存神雷</t>
+  </si>
+  <si>
+    <t>生存驱魔</t>
+  </si>
+  <si>
+    <t>生存剑网</t>
+  </si>
+  <si>
+    <t>生存火狱</t>
+  </si>
+  <si>
+    <t>生存剧毒</t>
+  </si>
+  <si>
+    <t>生存武盾</t>
+  </si>
+  <si>
+    <t>生存法盾</t>
+  </si>
+  <si>
+    <t>生存道盾</t>
+  </si>
+  <si>
+    <t>生存火麟</t>
+  </si>
+  <si>
+    <t>生存冰爆</t>
+  </si>
+  <si>
+    <t>生存英灵</t>
   </si>
 </sst>
 </file>
@@ -3146,61 +3167,462 @@
       <c r="H53" s="6"/>
     </row>
     <row r="54" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
+      <c r="C54" s="2">
+        <v>301</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E54" s="2">
+        <v>73</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="2">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="55" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
+      <c r="C55" s="2">
+        <v>302</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="2">
+        <v>73</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="2">
+        <v>2</v>
+      </c>
+      <c r="O55" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="56" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
+      <c r="C56" s="2">
+        <v>303</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" s="2">
+        <v>73</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="2">
+        <v>3</v>
+      </c>
+      <c r="O56" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+      <c r="C57" s="2">
+        <v>304</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" s="2">
+        <v>73</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="2">
+        <v>1</v>
+      </c>
+      <c r="O57" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
+      <c r="C58" s="2">
+        <v>305</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" s="2">
+        <v>73</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="2">
+        <v>2</v>
+      </c>
+      <c r="O58" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
+      <c r="C59" s="2">
+        <v>306</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E59" s="2">
+        <v>73</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="2">
+        <v>3</v>
+      </c>
+      <c r="O59" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="60" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
+      <c r="C60" s="2">
+        <v>307</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" s="2">
+        <v>73</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="2">
+        <v>1</v>
+      </c>
+      <c r="O60" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="61" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+      <c r="C61" s="2">
+        <v>308</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E61" s="2">
+        <v>73</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="2">
+        <v>2</v>
+      </c>
+      <c r="O61" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="62" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
+      <c r="C62" s="2">
+        <v>309</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" s="2">
+        <v>73</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="L62" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="2">
+        <v>3</v>
+      </c>
+      <c r="O62" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="63" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
+      <c r="C63" s="2">
+        <v>310</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E63" s="2">
+        <v>73</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="2">
+        <v>1</v>
+      </c>
+      <c r="O63" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="64" s="2" customFormat="1" customHeight="1" spans="3:15">
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A65" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="C64" s="2">
+        <v>311</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E64" s="2">
+        <v>73</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="2">
+        <v>2</v>
+      </c>
+      <c r="O64" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C65" s="2">
-        <v>110</v>
+        <v>312</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E65" s="2">
         <v>73</v>
@@ -3208,46 +3630,40 @@
       <c r="F65" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G65" s="7" t="s">
-        <v>45</v>
+      <c r="G65" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="M65" s="8" t="s">
         <v>51</v>
       </c>
       <c r="N65" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O65" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A66" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C66" s="2">
-        <v>111</v>
+        <v>313</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E66" s="2">
         <v>73</v>
@@ -3255,46 +3671,40 @@
       <c r="F66" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G66" s="7" t="s">
-        <v>45</v>
+      <c r="G66" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J66" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="M66" s="8" t="s">
         <v>51</v>
       </c>
       <c r="N66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A67" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:15">
       <c r="C67" s="2">
-        <v>112</v>
+        <v>314</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E67" s="2">
         <v>73</v>
@@ -3302,35 +3712,75 @@
       <c r="F67" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G67" s="7" t="s">
-        <v>45</v>
+      <c r="G67" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I67" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N67" s="2">
+        <v>2</v>
+      </c>
+      <c r="O67" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C68" s="2">
+        <v>315</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E68" s="2">
+        <v>73</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I68" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J67" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K67" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="L67" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="M67" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="N67" s="2">
+      <c r="J68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="2">
         <v>3</v>
       </c>
-      <c r="O67" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" customHeight="1"/>
+      <c r="O68" s="2">
+        <v>6</v>
+      </c>
+    </row>
     <row r="69" s="2" customFormat="1" customHeight="1"/>
     <row r="70" s="2" customFormat="1" customHeight="1"/>
     <row r="71" s="2" customFormat="1" customHeight="1"/>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="123">
   <si>
     <t>#</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>33,1007,1008</t>
+  </si>
+  <si>
+    <t>20,20,21,21</t>
   </si>
   <si>
     <t>生存神雷</t>
@@ -3186,7 +3189,7 @@
         <v>46</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="J54" s="8" t="s">
         <v>48</v>
@@ -3212,7 +3215,7 @@
         <v>302</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E55" s="2">
         <v>73</v>
@@ -3227,7 +3230,7 @@
         <v>46</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>48</v>
@@ -3253,7 +3256,7 @@
         <v>303</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E56" s="2">
         <v>73</v>
@@ -3268,7 +3271,7 @@
         <v>46</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>48</v>
@@ -3294,7 +3297,7 @@
         <v>304</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E57" s="2">
         <v>73</v>
@@ -3309,7 +3312,7 @@
         <v>46</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>48</v>
@@ -3335,7 +3338,7 @@
         <v>305</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E58" s="2">
         <v>73</v>
@@ -3350,7 +3353,7 @@
         <v>46</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="J58" s="8" t="s">
         <v>48</v>
@@ -3376,7 +3379,7 @@
         <v>306</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E59" s="2">
         <v>73</v>
@@ -3391,7 +3394,7 @@
         <v>46</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>48</v>
@@ -3417,7 +3420,7 @@
         <v>307</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E60" s="2">
         <v>73</v>
@@ -3432,7 +3435,7 @@
         <v>46</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="J60" s="8" t="s">
         <v>48</v>
@@ -3458,7 +3461,7 @@
         <v>308</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E61" s="2">
         <v>73</v>
@@ -3473,7 +3476,7 @@
         <v>46</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>48</v>
@@ -3499,7 +3502,7 @@
         <v>309</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E62" s="2">
         <v>73</v>
@@ -3514,7 +3517,7 @@
         <v>46</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>48</v>
@@ -3540,7 +3543,7 @@
         <v>310</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E63" s="2">
         <v>73</v>
@@ -3555,7 +3558,7 @@
         <v>46</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>48</v>
@@ -3581,7 +3584,7 @@
         <v>311</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E64" s="2">
         <v>73</v>
@@ -3596,7 +3599,7 @@
         <v>46</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="J64" s="8" t="s">
         <v>48</v>
@@ -3622,7 +3625,7 @@
         <v>312</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E65" s="2">
         <v>73</v>
@@ -3637,7 +3640,7 @@
         <v>46</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>48</v>
@@ -3663,7 +3666,7 @@
         <v>313</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E66" s="2">
         <v>73</v>
@@ -3678,7 +3681,7 @@
         <v>46</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="J66" s="8" t="s">
         <v>48</v>
@@ -3704,7 +3707,7 @@
         <v>314</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E67" s="2">
         <v>73</v>
@@ -3719,7 +3722,7 @@
         <v>46</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="J67" s="8" t="s">
         <v>48</v>
@@ -3745,7 +3748,7 @@
         <v>315</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E68" s="2">
         <v>73</v>
@@ -3760,7 +3763,7 @@
         <v>46</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J68" s="8" t="s">
         <v>48</v>
